--- a/internal_doc/05.测试设计/参数校验/测试用例/集群管理（组管理）参数校验测试用例.xlsx
+++ b/internal_doc/05.测试设计/参数校验/测试用例/集群管理（组管理）参数校验测试用例.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="76">
   <si>
     <t>name</t>
   </si>
@@ -80,13 +80,6 @@
   <si>
     <t>测试用例摘要（测试目的）</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>listCollections，加条件查询</t>
-  </si>
-  <si>
-    <t>语法：db.listCollections()
-无参数</t>
   </si>
   <si>
     <t>CreateCataRG，格式错误</t>
@@ -112,298 +105,235 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、CreateCataRG创建失败，提示参数错误，提示信息合理准确
-2、日志打印信息合理准确</t>
-  </si>
-  <si>
-    <t>1、CreateCataRG创建失败，提示CreateCataRG不存在，提示信息合理准确
-2、日志打印信息合理准确</t>
-  </si>
-  <si>
-    <t>1、CreateCataRG创建失败，提示系统CreateCataRG不能删除，提示信息合理准确
-2、日志打印信息合理准确</t>
-  </si>
-  <si>
-    <t>getCreateCataRG，获取不存在的CreateCataRG</t>
-  </si>
-  <si>
-    <t>语法：db.collectionspace.getCreateCataRG(&lt; name &gt;)
-参数规格：
-name：string，必填，获取已存在的CreateCataRG。不能获取系统CreateCataRG。</t>
-  </si>
-  <si>
-    <t>1、CreateCataRG获取失败，提示CreateCataRG不存在，提示信息合理准确
-2、日志打印信息合理准确</t>
-  </si>
-  <si>
-    <t>getCreateCataRG，指定的CreateCataRG名为空</t>
-  </si>
-  <si>
-    <t>1、进入sdb，获取指定的CreateCataRG，CreateCataRG名为空，覆盖如下取值：
-db.collectionspace.getCreateCataRG("")
-db.collectionspace.getCreateCataRG()
-2、检查执行结果</t>
-  </si>
-  <si>
-    <t>1、CreateCataRG获取失败，提示参数错误，提示信息合理准确
-2、日志打印信息合理准确</t>
-  </si>
-  <si>
-    <t>1、进入sdb，获取所有CreateCataRG（非系统CreateCataRG），指定CreateCataRG名，覆盖如下取值：
-  a.指定已存在的CreateCataRG名
-  b.空串
-如：
-db.listCollections("testCreateCataRG")，其中testCreateCataRG在sdb存在
-db.listCollections("")
-2、检查执行结果</t>
-  </si>
-  <si>
-    <t>1、CreateCataRG获取成功，指定的CreateCataRG被直接忽略，返回结果显示所有CreateCataRG（非系统CreateCataRG）</t>
-  </si>
-  <si>
-    <t>1、CreateCataRG创建成功，执行db.listReplicaGroups可以查看到新创建的CreateCataRG。
+    <t>CreateCataRG，Host指定的主机名/IP网络不通</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CreateCataRG，Host取值为空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CreateCataRG，Host取值无效</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CreateCataRG，Service取值为空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CreateCataRG，Service指定的端口被占用</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CreateCataRG，Service无效取值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CreateCataRG，Dbpath指定的目录没有写权限</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CreateCataRG，Dbpath无效取值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CreateCataRG，Dbpath取值为空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CreateCataRG，Config无效取值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>配置无效的config参数   ---参考创建节点config配置（吴艳）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CreateCataRG，Config取值为空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CreateCataRG，参数格式错误</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>removeCataRG，删除为空的CataRG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，删除为空的CataRG，如：
+db.removeCatalogRG()，其中CM只有一个为空的CataRG
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CataRG创建成功，执行db.listReplicaGroups可以查看到新创建的CreateCataRG。
 检查Config默认取值正确。
 2、在新创建的CreateCataRG下创建节点，节点创建成功，且可用正常启停；创建CS、CL并插入数据，数据插入成功。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CreateCataRG，Host指定的主机名/IP网络不通</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CreateCataRG，Host取值为空</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，创建CreateCataRG，指定的主机名/IP网络不通，覆盖如下取值：
+  </si>
+  <si>
+    <t>1、CataRG创建失败，提示配置的Host网络不通，提示信息合理准确
+2、日志打印信息合理准确</t>
+  </si>
+  <si>
+    <t>1、CataRG创建失败，提示参数错误，提示信息合理准确
+2、日志打印信息合理准确</t>
+  </si>
+  <si>
+    <t>1、CataRG创建失败，提示端口被占用，提示信息合理准确
+2、查看端口
+2、日志打印信息合理准确</t>
+  </si>
+  <si>
+    <t>1、CataRG创建失败，提示权限不够，提示信息合理准确
+2、日志打印信息合理准确</t>
+  </si>
+  <si>
+    <t>removeCataRG，删除的CataRG包含数据节点信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>removeCataRG，删除的CataRG包含协调节点信息</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，删除的CataRG包含数据节点信息，如：
+db.removeCatalogRG(),其中编目组包含数据节点信息
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，删除的CataRG包含数据节点信息，如：
+db.removeCatalogRG(),其中编目组包含协调节点信息
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>removeCataRG，带条件删除</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>带条件删除，如removeCataRG
+语法：db.removeCataRG("group1")</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CataRG删除成功，执行db.listReplicaGroups可以查看到CataRG已被删除
+2、查看CataRG相关配置文件已删除干净</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，带条件删除，如：
+db.removeCatalogRG("SYSCatalogGroup")
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CataRG删除失败，提示CataRG包含数据/协调节点信息不能删除，提示信息合理准确
+2、日志打印信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语法：
+db.getCatalogRG()
+只能获取存在的组</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>getCataRG，获取存在的组</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CataRG，输入Host、Service、Dbpath、Config有效参数创建CataRG，规格如下：
+Host覆盖如下取值：
+  a.正常通信的主机名，如：test
+  b.正常通信的IP地址，如：192.168.8.9
+  c.指定主机名为localhost
+Service覆盖如下取值：
+  a.端口未被占用，如配置未被占用的11800端口
+  b.往后顺延的3个端口未被占用，如配置11800端口，11801/11801/11803端口未被占用
+  c.有效取值：0、65535
+  d.服务名（已配置端口对应服务名）
+Dbpath覆盖如下取值：
+  a.路径存在，且有写权限
+  b.路径不存在，上级目录有写权限，如指定目录为/opt/sequoiadb，用户对/opt有写权限
+Host覆盖如下取值：
+  a.不配置config
+  b.参见数据库配置一节，配置有效参数   ---参考创建节点config配置（吴艳）  --跟创建节点交叉测试
+2、检查执行结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CataRG，指定的主机名/IP网络不通，覆盖如下取值：
   a.无法连接的主机名，如:test（test主机跟处理主机网络不通）
   b.无法连接的IP，如1.1.1.1（1.1.1.1与处理主机网络不通）
   c.无效的IP地址，如192.168.*
 如：
 db.createCataRG("1.1.1.1",11800,"/data/11800")
 2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、CreateCataRG创建失败，提示配置的Host网络不通，提示信息合理准确
-2、日志打印信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CreateCataRG，Host取值无效</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，创建CreateCataRG，Host取值无效，如：
+  </si>
+  <si>
+    <t>1、进入sdb，创建CataRG，Host取值无效，如：
 db.createCataRG("1.1.*",11800,"/data/11800")
 2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，创建CreateCataRG，Host取值为空，如：
+  </si>
+  <si>
+    <t>1、进入sdb，创建CataRG，Host取值为空，如：
 db.createCataRG("",11800,"/data/11800")
 db.createCataRG(,11800,"/data/11800")
 2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CreateCataRG，Service取值为空</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CreateCataRG，Service指定的端口被占用</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，创建CreateCataRG，Service指定的端口被占用，覆盖如下取值：
+  </si>
+  <si>
+    <t>1、进入sdb，创建CataRG，Service指定的端口被占用，覆盖如下取值：
   a.指定的端口被占用
   b.往后顺延的3个端口中其中1个端口被占用
 如：
 db.createCataRG("test",11800,"/data/11800")，其中11800端口被占用
 db.createCataRG("test",11800,"/data/11800")，其中11802端口被占用
 2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、CreateCataRG创建失败，提示端口被占用，提示信息合理准确
-2、查看端口
-2、日志打印信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1、进入sdb，创建CreateCataRG，输入Host、Service、Dbpath、Config有效参数创建CreateCataRG，规格如下：
-Host覆盖如下取值：
-  a.正常通信的主机名，如：test
-  b.正常通信的IP地址，如：192.168.8.9
-  c.指定主机名为</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>localhost</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-Service覆盖如下取值：
-  a.端口未被占用，如配置未被占用的11800端口
-  b.往后顺延的3个端口未被占用，如配置11800端口，11801/11801/11803端口未被占用
-  c.有效取值：0、65535
-  d.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>服务名</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>（已配置端口对应服务名）
-Dbpath覆盖如下取值：
-  a.路径存在，且有写权限
-  b.路径不存在，上级目录有写权限，如指定目录为/opt/sequoiadb，用户对/opt有写权限
-Host覆盖如下取值：
-  a.不配置config
-  b.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>参见数据库配置一节，配置有效参数   ---参考创建节点config配置（吴艳）  --跟创建节点交叉测试</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-2、检查执行结果</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CreateCataRG，Service无效取值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，创建CreateCataRG，Service无效取值，如：
+  </si>
+  <si>
+    <t>1、进入sdb，创建CataRG，Service无效取值，如：
   取值为test123*、-1、65536
 如：
 db.createCataRG("test","test123*","/data/11800")
 db.createCataRG("test",-1,"/data/11800")
 db.createCataRG("test",65536,"/data/11800")
 2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，创建CreateCataRG，Service取值为空，如：
+  </si>
+  <si>
+    <t>1、进入sdb，创建CataRG，Service取值为空，如：
 db.createCataRG("test","","/data/11800")
 db.createCataRG("test",,"/data/11800")
 2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CreateCataRG，Dbpath指定的目录没有写权限</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CreateCataRG，Dbpath无效取值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CreateCataRG，Dbpath取值为空</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、sdbadmin用户进入sdb，创建CreateCataRG，Dbpath指定的目录没有写权限，如：
+  </si>
+  <si>
+    <t>1、sdbadmin用户进入sdb，创建CataRG，Dbpath指定的目录没有写权限，如：
 db.createCataRG("test","11800","/data/11800")，其中/data对sdbadmin没有写权限
 2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、CreateCataRG创建失败，提示权限不够，提示信息合理准确
-2、日志打印信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，创建CreateCataRG，Dbpath无效取值，覆盖如下取值：
+  </si>
+  <si>
+    <t>1、进入sdb，创建CataRG，Dbpath无效取值，覆盖如下取值：
   a.目录名无效，如/date/test123@#
   b.路径无效，如不带路径标记”/”（opt）
 如：
 db.createCataRG("test",11800,"/date/test123@#")
 db.createCataRG("test",11800,"date/11800")
 2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，创建CreateCataRG，Service取值为空，如：
+  </si>
+  <si>
+    <t>1、进入sdb，创建CataRG，Service取值为空，如：
 db.createCataRG("test",11800,"")
 db.createCataRG("test",11800,)
 2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CreateCataRG，Config无效取值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>配置无效的config参数   ---参考创建节点config配置（吴艳）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CreateCataRG，Config取值为空</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，创建CreateCataRG，Service取值为空，如：
+  </si>
+  <si>
+    <t>1、进入sdb，创建CataRG，Service取值为空，如：
 db.createCataRG("test",11800,"/date/11800",[""])
 db.createCataRG("test",11800,"/date/11800",[])
 2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CreateCataRG，参数格式错误</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，创建CreateCataRG，参数格式错误，覆盖如下取值：
+  </si>
+  <si>
+    <t>1、进入sdb，创建CataRG，参数格式错误，覆盖如下取值：
   a.引号使用错误，如字符串类型不带引号输入、int类型带引号输入
   b.多参数
   c.为空
@@ -411,111 +341,22 @@
 db.testCS.CreateCataRG("testCreateCataRG",{ShardingKey:{"age":1,ShardingType:"hash",Partition:4}) 
 db.testCS.CreateCataRG("testCreateCataRG",{ShardingKey:{"age":1,ShardingType:"range",Partition:1024}) 
 2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1、进入sdb，创建CreateCataRG，参数格式错误，覆盖如下参数格式：
+  </si>
+  <si>
+    <t>1、进入sdb，创建CataRG，参数格式错误，覆盖如下参数格式：
   a.引号使用错误，如字符串类型不带引号输入、bool类型带引号输入
   b.多参数
   c.为空
 如：
-db.createCataRG("test","11800",/date/11800,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[config]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)
-db.createCataRG("test","11800",/date/11800,</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>[config]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>,01)
-db.createCataRG(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>)
-2、检查执行结果</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，删除不存在的CreateCataRG，如：
-db.testCS.removeCataRG("testCreateCataRG"),其中testCreateCataRG在sdb不存在
-2、检查执行结果</t>
-  </si>
-  <si>
-    <t>1、进入sdb，删除系统CreateCataRG，如：
-db.testCS.removeCataRG("testCreateCataRG"),其中testCreateCataRG为系统CreateCataRG
-2、检查执行结果</t>
-  </si>
-  <si>
-    <t>removeCataRG，指定CreateCataRG名为空</t>
-  </si>
-  <si>
-    <t>1、进入sdb，删除CreateCataRG，CreateCataRG名为空，覆盖如下取值：
-db.testCS.removeCataRG("")
-db.testCS.removeCataRG()
-2、检查执行结果</t>
-  </si>
-  <si>
-    <t>1、进入sdb，获取指定CreateCataRG，不指定CreateCataRG名，如：
-db.testCS.removeCataRG("testCreateCataRG")，其中testCreateCataRG在sdb不存在
-2、检查执行结果</t>
-  </si>
-  <si>
-    <t>removeCataRG，删除不存在的CataRG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>removeCataRG，删除系统CataRG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>removeCataRG，删除为空的CataRG</t>
+db.createCataRG("test","11800",/date/11800,[config])
+db.createCataRG("test","11800",/date/11800,[config],01)
+db.createCataRG()
+2、检查执行结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，获取CataRG，如：
+db.getCatalogRG()，其中CM中至少有一个编目组
+2、检查执行结果</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -525,19 +366,42 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、空组
-2、编目组包含编目节点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，删除为空的CataRG，如：
-db.removeCatalogRG()，其中CM只有一个为空的CataRG
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、CataRG删除成功，db.list(4)或db.list(5)查看CreateCataRG以及CreateCataRG下CreateCataRG已全部删除
-2、查看CreateCataRG相关配置文件已删除干净</t>
+    <t>1、CM运行正常
+2、CM至少存在一个CataRG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>getCataRG，带条件查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，带条件查询，如：
+db.getCatalogRG("SYSCatalogGroup")
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CataRG获取成功，指定的CataRG被直接忽略，返回结果显示所有的CataRG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CataRG删除成功，指定的CataRG被直接忽略，执行db.listReplicaGroups可以查看到CataRG已被删除
+2、查看CataRG相关配置文件已删除干净</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>listReplicaGroups，带条件查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语法：db.listReplicaGroups()
+无参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，获取所有CataRG，带条件查询，如：
+db.listReplicaGroups("SYSCatalogGroup")
+2、检查执行结果</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1104,13 +968,13 @@
     </row>
     <row r="3" spans="1:9" ht="174" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D3" s="4">
         <v>1</v>
@@ -1122,10 +986,10 @@
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="I3" s="4">
         <v>1</v>
@@ -1133,10 +997,10 @@
     </row>
     <row r="4" spans="1:9" ht="148.5">
       <c r="A4" s="2" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D4" s="4">
         <v>1</v>
@@ -1144,73 +1008,73 @@
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="I4" s="4"/>
     </row>
-    <row r="5" spans="1:9" ht="67.5">
+    <row r="5" spans="1:9" ht="54">
       <c r="A5" s="2" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="2" t="s">
-        <v>41</v>
+        <v>55</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I5" s="4"/>
     </row>
-    <row r="6" spans="1:9" ht="67.5">
+    <row r="6" spans="1:9" ht="54">
       <c r="A6" s="2" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="2" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I6" s="4"/>
     </row>
     <row r="7" spans="1:9" ht="135">
       <c r="A7" s="2" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="2" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="I7" s="4"/>
     </row>
-    <row r="8" spans="1:9" ht="121.5">
+    <row r="8" spans="1:9" ht="108">
       <c r="A8" s="2" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D8" s="4">
         <v>1</v>
@@ -1218,20 +1082,20 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I8" s="4"/>
     </row>
-    <row r="9" spans="1:9" ht="67.5">
+    <row r="9" spans="1:9" ht="54">
       <c r="A9" s="2" t="s">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D9" s="4">
         <v>1</v>
@@ -1239,19 +1103,19 @@
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="2" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I9" s="4"/>
     </row>
     <row r="10" spans="1:9" ht="67.5">
       <c r="A10" s="2" t="s">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D10" s="4">
         <v>1</v>
@@ -1259,19 +1123,19 @@
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="2" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="I10" s="4"/>
     </row>
     <row r="11" spans="1:9" ht="121.5">
       <c r="A11" s="2" t="s">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D11" s="4">
         <v>1</v>
@@ -1279,37 +1143,37 @@
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="G11" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I11" s="4"/>
     </row>
-    <row r="12" spans="1:9" ht="67.5">
+    <row r="12" spans="1:9" ht="54">
       <c r="A12" s="2" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I12" s="4"/>
     </row>
     <row r="13" spans="1:9" ht="40.5">
       <c r="A13" s="2" t="s">
-        <v>58</v>
+        <v>31</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D13" s="4">
         <v>1</v>
@@ -1317,37 +1181,37 @@
       <c r="E13" s="4"/>
       <c r="F13" s="4"/>
       <c r="G13" s="8" t="s">
-        <v>59</v>
+        <v>32</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I13" s="4"/>
     </row>
-    <row r="14" spans="1:9" ht="94.5">
+    <row r="14" spans="1:9" ht="81">
       <c r="A14" s="2" t="s">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
       <c r="G14" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I14" s="4"/>
     </row>
     <row r="15" spans="1:9" ht="189">
       <c r="A15" s="2" t="s">
-        <v>62</v>
+        <v>34</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D15" s="4">
         <v>1</v>
@@ -1355,19 +1219,19 @@
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I15" s="4"/>
     </row>
     <row r="16" spans="1:9" ht="175.5">
       <c r="A16" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D16" s="4">
         <v>1</v>
@@ -1375,22 +1239,22 @@
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I16" s="4"/>
     </row>
     <row r="17" spans="1:9" ht="81">
       <c r="A17" s="2" t="s">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="D17" s="4">
         <v>1</v>
@@ -1398,22 +1262,20 @@
       <c r="E17" s="4"/>
       <c r="F17" s="4"/>
       <c r="G17" s="2" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="I17" s="4"/>
     </row>
     <row r="18" spans="1:9" ht="54">
       <c r="A18" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B18" s="6" t="s">
-        <v>74</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="B18" s="6"/>
       <c r="C18" s="1" t="s">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="D18" s="4">
         <v>1</v>
@@ -1421,102 +1283,107 @@
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
       <c r="G18" s="2" t="s">
-        <v>65</v>
+        <v>44</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I18" s="4"/>
     </row>
     <row r="19" spans="1:9" ht="54">
       <c r="A19" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="I19" s="4"/>
+    </row>
+    <row r="20" spans="1:9" ht="54">
+      <c r="A20" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D20" s="4">
+        <v>1</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="54">
+      <c r="A21" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="D21" s="4">
+        <v>1</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" ht="40.5">
+      <c r="A22" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B22" s="6"/>
+      <c r="C22" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="4">
+        <v>1</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H22" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D19" s="4">
-        <v>1</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="67.5">
-      <c r="A20" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D20" s="4">
-        <v>1</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="108">
-      <c r="A21" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D21" s="4">
-        <v>1</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="67.5">
-      <c r="A22" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D22" s="4">
-        <v>1</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="135">
+    </row>
+    <row r="23" spans="1:9" ht="40.5">
       <c r="A23" s="2" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D23" s="4">
         <v>1</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>34</v>
+        <v>71</v>
       </c>
     </row>
     <row r="24" spans="1:9">

--- a/internal_doc/05.测试设计/参数校验/测试用例/集群管理（组管理）参数校验测试用例.xlsx
+++ b/internal_doc/05.测试设计/参数校验/测试用例/集群管理（组管理）参数校验测试用例.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="122">
   <si>
     <t>name</t>
   </si>
@@ -167,11 +167,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、CataRG创建成功，执行db.listReplicaGroups可以查看到新创建的CreateCataRG。
-检查Config默认取值正确。
-2、在新创建的CreateCataRG下创建节点，节点创建成功，且可用正常启停；创建CS、CL并插入数据，数据插入成功。</t>
-  </si>
-  <si>
     <t>1、CataRG创建失败，提示配置的Host网络不通，提示信息合理准确
 2、日志打印信息合理准确</t>
   </si>
@@ -210,11 +205,6 @@
   </si>
   <si>
     <t>removeCataRG，带条件删除</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>带条件删除，如removeCataRG
-语法：db.removeCataRG("group1")</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -375,12 +365,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、进入sdb，带条件查询，如：
-db.getCatalogRG("SYSCatalogGroup")
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、CataRG获取成功，指定的CataRG被直接忽略，返回结果显示所有的CataRG</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -394,14 +378,281 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>语法：db.listReplicaGroups()
+    <t>CreateCoordRG，带条件创建</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语法：
+db.listReplicaGroups()
 无参数</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>1、进入sdb，获取所有CataRG，带条件查询，如：
-db.listReplicaGroups("SYSCatalogGroup")
-2、检查执行结果</t>
+db.listReplicaGroups("testCatalogGroup")
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CoordRG获取成功，指定的CoordRG被直接忽略，创建SYSCoord组创建成功，执行db.listReplicaGroups可以查看到已创建的coord组。
+2、在新创建的CoordRG下创建节点，节点创建成功，且可用正常启停，节点可正常连接</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语法：
+db.createCoordRG()
+无参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语法：
+db.removeCoordRG()，无参数
+删除协调分区组，原则上会把该分区组的所有协调节点都删除</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>removeCoordRG()，删除为空和不为空的组</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CoordRG，带条件查询，如：
+db.createCoordRG("testCoordRG")
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，删除CoordRG，覆盖如下取值：
+   a.CoordRG为空
+   b.CoordRG有至少一个Coord节点，组不为空
+执行removeCoordRG()
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CoordRG删除成功，组下的节点也一并删除，执行db.listReplicaGroups可以查看到CoordRG已被删除
+2、查看CoordRG相关配置文件已删除干净</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，带条件查询，如：
+db.getCatalogRG("testCatalogGroup")
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>removeCoordRG()，带条件删除</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，带条件删除，如：
+db.removeCoordRG("testCoordRG")
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CoordRG删除成功，指定的CoordRG被直接忽略，执行db.listReplicaGroups可以查看到CoordRG已被删除
+2、查看CoordRG相关配置文件已删除干净</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语法：
+db.createRG(&lt;name&gt;)
+string,必填，同一个数据库对象中，分区组名唯一。name不能是空串，含点（.）或者美元符号（$），并且长度不能超过127B。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createRG，覆盖name有效字符和边界</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建RG，输入name有效参数创建RG，规格如下：
+name覆盖如下取值：
+  a.1字节的有效字符，如：a 或 *
+  b.127字节的有效字符，覆盖所有支持的有效字符，如：“123-test-中文。~!@#%^&amp;*()_+-=\][{}|,/&lt;&gt;?~·！@#￥%……&amp;*（）——+《》{}|【】、，。、~_127B”
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>removeRG，删除不存在的组</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CM运行正常
+2、CM至少存在一个RG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，删除不存在的RG，如：
+db.removeRG("test")，其中test组不存在
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、RG删除失败，提示test组不存在，执行db.listReplicaGroups其他已存在的RG不会被删除
+2、日志打印信息合理正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createRG，name字符无效</t>
+  </si>
+  <si>
+    <t>createRG，name长度无效</t>
+  </si>
+  <si>
+    <t>createRG，name重复</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1、首次创建name唯一RG，创建成功
+2、重复创建相同name的RG，创建失败，返回结果报错，并提示RG名已存在，提示信息合理准确
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CataRG创建成功，执行db.listReplicaGroups可以查看到新创建的CataRG。
+检查Config默认取值正确。
+2、在新创建的CataRG下创建节点，节点创建成功，且可用正常启停；创建CS、RG并插入数据，数据插入成功。</t>
+  </si>
+  <si>
+    <t>1、RG创建成功，执行db.listReplicaGroups可以查看到新创建的RG。
+2、在新创建的CataRG下创建节点，节点创建成功，且可用正常启停；创建CS、RG并插入数据，数据插入成功。
+切分数据，数据可以切分成功；同步数据，数据可以同步成功；</t>
+  </si>
+  <si>
+    <t>1、进入sdb，创建RG，输入有效的name创建RG，如：
+db.createRG("testRG")
+2、重复步骤1，创建name相同的RG
+3、检查执行结果</t>
+  </si>
+  <si>
+    <t>1、RG创建失败，提示参数不合法，提示信息合理准确
+2、日志打印信息合理准确</t>
+  </si>
+  <si>
+    <t>1、RG创建失败，提示参数超出长度，提示信息合理准确
+2、日志打印信息合理准确</t>
+  </si>
+  <si>
+    <t>1、进入sdb，创建RG，输入name长度无效，覆盖如下无效取值：
+  a.空串
+  b.128字节
+如：
+db.createRG('')  或  db.createRG()   或  为128字节的有效字符
+3、检查执行结果</t>
+  </si>
+  <si>
+    <t>createRG，格式错误</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建RG，格式错误，如：
+db.createRG()
+db.createRG("testRG","testRG2",123)
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>removeRG，name为空</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建RG，输入name字符无效，覆盖如下无效取值：
+  a.包含（.）
+  b.包含$
+如：
+db.createRG('test.RG')
+db.createRG('test$RG')
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，删除RG，name为空，如：
+db.removeRG("")
+db.removeRG()
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、RG创建失败，提示参数错误，提示信息合理准确
+2、日志打印信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、RG删除失败，提示参数错误，提示信息合理准确
+2、日志打印信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>removeRG，格式错误</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，删除RG，格式错误，如：
+db.removeRG()
+db.removeRG("testRG","testRG2",123)
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+语法：
+db.removeRG(&lt;name&gt;)
+删除存在的组</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+语法：
+db.startRG(&lt;name&gt;)
+参数规格：
+name：string，必填
+指定的分区组名必须存在，不然返回异常；如果指定的分区组已经启动，再使用该方法同样会出现异常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>startRG,name取值为空串</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>startRG,start已启动的组</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>startRG,start不存在的组</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、RG重复启动失败，提示组已启动，提示信息合理准确
+2、日志打印信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，startRG,start已启动的组，如：
+db.startRG("group1")，其中group1为启动状态
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，startRG,start不存在的组，如：
+db.startRG("group4")，其中group4不存在
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、RG启动失败，提示组不存在，提示信息合理准确
+2、日志打印信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，startRG,name取值为空串，如：
+db.startRG()
+db.startRG("")
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、RG启动失败，提示参数错误，提示信息合理准确
+2、日志打印信息合理准确</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -575,8 +826,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I23" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
-  <autoFilter ref="A1:I23"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I37" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
+  <autoFilter ref="A1:I37"/>
   <tableColumns count="9">
     <tableColumn id="1" uniqueName="name" name="name" dataDxfId="8">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/@name" xmlDataType="string"/>
@@ -895,7 +1146,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I27"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="26.375" style="1" customWidth="1"/>
@@ -986,10 +1237,10 @@
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>37</v>
+        <v>96</v>
       </c>
       <c r="I3" s="4">
         <v>1</v>
@@ -1008,10 +1259,10 @@
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
       <c r="G4" s="2" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I4" s="4"/>
     </row>
@@ -1026,10 +1277,10 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I5" s="4"/>
     </row>
@@ -1044,10 +1295,10 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I6" s="4"/>
     </row>
@@ -1062,10 +1313,10 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I7" s="4"/>
     </row>
@@ -1082,10 +1333,10 @@
       <c r="E8" s="4"/>
       <c r="F8" s="4"/>
       <c r="G8" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I8" s="4"/>
     </row>
@@ -1103,10 +1354,10 @@
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I9" s="4"/>
     </row>
@@ -1123,10 +1374,10 @@
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
       <c r="G10" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I10" s="4"/>
     </row>
@@ -1143,10 +1394,10 @@
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
       <c r="G11" s="2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I11" s="4"/>
     </row>
@@ -1161,10 +1412,10 @@
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
       <c r="G12" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I12" s="4"/>
     </row>
@@ -1184,7 +1435,7 @@
         <v>32</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I13" s="4"/>
     </row>
@@ -1199,10 +1450,10 @@
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
       <c r="G14" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I14" s="4"/>
     </row>
@@ -1219,10 +1470,10 @@
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
       <c r="G15" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I15" s="4"/>
     </row>
@@ -1239,10 +1490,10 @@
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
       <c r="G16" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I16" s="4"/>
     </row>
@@ -1251,10 +1502,10 @@
         <v>35</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D17" s="4">
         <v>1</v>
@@ -1265,17 +1516,17 @@
         <v>36</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I17" s="4"/>
     </row>
     <row r="18" spans="1:9" ht="54">
       <c r="A18" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D18" s="4">
         <v>1</v>
@@ -1283,120 +1534,348 @@
       <c r="E18" s="4"/>
       <c r="F18" s="4"/>
       <c r="G18" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I18" s="4"/>
     </row>
     <row r="19" spans="1:9" ht="54">
       <c r="A19" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
       <c r="F19" s="4"/>
       <c r="G19" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="I19" s="4"/>
     </row>
     <row r="20" spans="1:9" ht="54">
       <c r="A20" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B20" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D20" s="4">
+        <v>1</v>
+      </c>
+      <c r="G20" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C20" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D20" s="4">
-        <v>1</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="H20" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="54">
       <c r="A21" s="2" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D21" s="4">
         <v>1</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="40.5">
       <c r="A22" s="2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="1" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
       <c r="D22" s="4">
         <v>1</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="40.5">
       <c r="A23" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="4">
+        <v>1</v>
+      </c>
+      <c r="G23" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="H23" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="94.5">
+      <c r="A24" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H24" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D23" s="4">
-        <v>1</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
-      <c r="A24" s="2"/>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25" s="2"/>
-    </row>
-    <row r="26" spans="1:9">
-      <c r="A26" s="2"/>
-    </row>
-    <row r="27" spans="1:9">
-      <c r="A27" s="2"/>
+      <c r="I24" s="4"/>
+    </row>
+    <row r="25" spans="1:9" ht="67.5">
+      <c r="A25" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" ht="81">
+      <c r="A26" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D26" s="4">
+        <v>1</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" ht="121.5">
+      <c r="A27" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="67.5">
+      <c r="A28" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="4">
+        <v>1</v>
+      </c>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="I28" s="4"/>
+    </row>
+    <row r="29" spans="1:9" ht="108">
+      <c r="A29" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D29" s="4">
+        <v>1</v>
+      </c>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I29" s="4"/>
+    </row>
+    <row r="30" spans="1:9" ht="108">
+      <c r="A30" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B30" s="7"/>
+      <c r="C30" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D30" s="4">
+        <v>1</v>
+      </c>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="I30" s="4"/>
+    </row>
+    <row r="31" spans="1:9" ht="54">
+      <c r="A31" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="4">
+        <v>1</v>
+      </c>
+      <c r="E31" s="4"/>
+      <c r="F31" s="4"/>
+      <c r="G31" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="I31" s="4"/>
+    </row>
+    <row r="32" spans="1:9" ht="67.5">
+      <c r="A32" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="54">
+      <c r="A33" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="54">
+      <c r="A34" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="121.5">
+      <c r="A35" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="40.5">
+      <c r="A36" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="54">
+      <c r="A37" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>121</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/internal_doc/05.测试设计/参数校验/测试用例/集群管理（组管理）参数校验测试用例.xlsx
+++ b/internal_doc/05.测试设计/参数校验/测试用例/集群管理（组管理）参数校验测试用例.xlsx
@@ -13,6 +13,167 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>Author</author>
+  </authors>
+  <commentList>
+    <comment ref="A3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+OMA</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>上面需要覆盖参数校验
+优先验证</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>OMA</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>，</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>CM</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>优先级放低</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A9" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+跟上面用例合并</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A23" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+参数格式错误</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A34" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Author:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+添加热备组用例</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
 <connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <connection id="1" name="testcase" type="4" refreshedVersion="0" background="1">
@@ -82,82 +243,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>CreateCataRG，格式错误</t>
-  </si>
-  <si>
-    <t>语法：db.createCataRG(&lt;host&gt;,&lt;service&gt;,&lt;dbpath&gt;,[config])
-格式：{"&lt;主机名/主机IP&gt;",&lt;端口号&gt;,"&lt;数据文件路径&gt;",[数据库配置参数对象]}
-参数规格：
-Host：string，必填,主机通信正常
-Service：int，必填，端口不被占用，包括往后顺延的3个端口。端口取值范围（0~65535）
-Dbpath：string，必填，需确保数据管理员（安装时创建，默认为 sdbadmin）用户有写权限。
-路径不存在会自动创建
-Config：Json对象，非必填
-参见数据库配置一节</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、CM运行正常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CreateCataRG，覆盖Host/Service/Dbpath/Config有效字符和边界</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CreateCataRG，Host指定的主机名/IP网络不通</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CreateCataRG，Host取值为空</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CreateCataRG，Host取值无效</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CreateCataRG，Service取值为空</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CreateCataRG，Service指定的端口被占用</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CreateCataRG，Service无效取值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CreateCataRG，Dbpath指定的目录没有写权限</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CreateCataRG，Dbpath无效取值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CreateCataRG，Dbpath取值为空</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CreateCataRG，Config无效取值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>配置无效的config参数   ---参考创建节点config配置（吴艳）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CreateCataRG，Config取值为空</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CreateCataRG，参数格式错误</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>removeCataRG，删除为空的CataRG</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -184,14 +270,6 @@
 2、日志打印信息合理准确</t>
   </si>
   <si>
-    <t>removeCataRG，删除的CataRG包含数据节点信息</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>removeCataRG，删除的CataRG包含协调节点信息</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、进入sdb，删除的CataRG包含数据节点信息，如：
 db.removeCatalogRG(),其中编目组包含数据节点信息
 2、检查执行结果</t>
@@ -201,10 +279,6 @@
     <t>1、进入sdb，删除的CataRG包含数据节点信息，如：
 db.removeCatalogRG(),其中编目组包含协调节点信息
 2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>removeCataRG，带条件删除</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -230,7 +304,277 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>getCataRG，获取存在的组</t>
+    <t>1、进入sdb，创建CataRG，指定的主机名/IP网络不通，覆盖如下取值：
+  a.无法连接的主机名，如:test（test主机跟处理主机网络不通）
+  b.无法连接的IP，如1.1.1.1（1.1.1.1与处理主机网络不通）
+  c.无效的IP地址，如192.168.*
+如：
+db.createCataRG("1.1.1.1",11800,"/data/11800")
+2、检查执行结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CataRG，Host取值无效，如：
+db.createCataRG("1.1.*",11800,"/data/11800")
+2、检查执行结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CataRG，Host取值为空，如：
+db.createCataRG("",11800,"/data/11800")
+db.createCataRG(,11800,"/data/11800")
+2、检查执行结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CataRG，Service指定的端口被占用，覆盖如下取值：
+  a.指定的端口被占用
+  b.往后顺延的3个端口中其中1个端口被占用
+如：
+db.createCataRG("test",11800,"/data/11800")，其中11800端口被占用
+db.createCataRG("test",11800,"/data/11800")，其中11802端口被占用
+2、检查执行结果</t>
+  </si>
+  <si>
+    <t>1、sdbadmin用户进入sdb，创建CataRG，Dbpath指定的目录没有写权限，如：
+db.createCataRG("test","11800","/data/11800")，其中/data对sdbadmin没有写权限
+2、检查执行结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CataRG，Service取值为空，如：
+db.createCataRG("test",11800,"")
+db.createCataRG("test",11800,)
+2、检查执行结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CataRG，Service取值为空，如：
+db.createCataRG("test",11800,"/date/11800",[""])
+db.createCataRG("test",11800,"/date/11800",[])
+2、检查执行结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CataRG，参数格式错误，覆盖如下参数格式：
+  a.引号使用错误，如字符串类型不带引号输入、bool类型带引号输入
+  b.多参数
+  c.为空
+如：
+db.createCataRG("test","11800",/date/11800,[config])
+db.createCataRG("test","11800",/date/11800,[config],01)
+db.createCataRG()
+2、检查执行结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，获取CataRG，如：
+db.getCatalogRG()，其中CM中至少有一个编目组
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CM运行正常
+2、CM至少存在一个CataRG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CataRG获取成功，指定的CataRG被直接忽略，返回结果显示所有的CataRG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CataRG删除成功，指定的CataRG被直接忽略，执行db.listReplicaGroups可以查看到CataRG已被删除
+2、查看CataRG相关配置文件已删除干净</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语法：
+db.listReplicaGroups()
+无参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CoordRG获取成功，指定的CoordRG被直接忽略，创建SYSCoord组创建成功，执行db.listReplicaGroups可以查看到已创建的coord组。
+2、在新创建的CoordRG下创建节点，节点创建成功，且可用正常启停，节点可正常连接</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语法：
+db.createCoordRG()
+无参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语法：
+db.removeCoordRG()，无参数
+删除协调分区组，原则上会把该分区组的所有协调节点都删除</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CoordRG，带条件查询，如：
+db.createCoordRG("testCoordRG")
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，删除CoordRG，覆盖如下取值：
+   a.CoordRG为空
+   b.CoordRG有至少一个Coord节点，组不为空
+执行removeCoordRG()
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CoordRG删除成功，组下的节点也一并删除，执行db.listReplicaGroups可以查看到CoordRG已被删除
+2、查看CoordRG相关配置文件已删除干净</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，带条件查询，如：
+db.getCatalogRG("testCatalogGroup")
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，带条件删除，如：
+db.removeCoordRG("testCoordRG")
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CoordRG删除成功，指定的CoordRG被直接忽略，执行db.listReplicaGroups可以查看到CoordRG已被删除
+2、查看CoordRG相关配置文件已删除干净</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CM运行正常
+2、CM至少存在一个RG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，删除不存在的RG，如：
+db.removeRG("test")，其中test组不存在
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、RG删除失败，提示test组不存在，执行db.listReplicaGroups其他已存在的RG不会被删除
+2、日志打印信息合理正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">1、首次创建name唯一RG，创建成功
+2、重复创建相同name的RG，创建失败，返回结果报错，并提示RG名已存在，提示信息合理准确
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CataRG创建成功，执行db.listReplicaGroups可以查看到新创建的CataRG。
+检查Config默认取值正确。
+2、在新创建的CataRG下创建节点，节点创建成功，且可用正常启停；创建CS、RG并插入数据，数据插入成功。</t>
+  </si>
+  <si>
+    <t>1、RG创建成功，执行db.listReplicaGroups可以查看到新创建的RG。
+2、在新创建的CataRG下创建节点，节点创建成功，且可用正常启停；创建CS、RG并插入数据，数据插入成功。
+切分数据，数据可以切分成功；同步数据，数据可以同步成功；</t>
+  </si>
+  <si>
+    <t>1、进入sdb，创建RG，输入有效的name创建RG，如：
+db.createRG("testRG")
+2、重复步骤1，创建name相同的RG
+3、检查执行结果</t>
+  </si>
+  <si>
+    <t>1、RG创建失败，提示参数不合法，提示信息合理准确
+2、日志打印信息合理准确</t>
+  </si>
+  <si>
+    <t>1、RG创建失败，提示参数超出长度，提示信息合理准确
+2、日志打印信息合理准确</t>
+  </si>
+  <si>
+    <t>1、进入sdb，创建RG，输入name长度无效，覆盖如下无效取值：
+  a.空串
+  b.128字节
+如：
+db.createRG('')  或  db.createRG()   或  为128字节的有效字符
+3、检查执行结果</t>
+  </si>
+  <si>
+    <t>1、进入sdb，创建RG，格式错误，如：
+db.createRG()
+db.createRG("testRG","testRG2",123)
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建RG，输入name字符无效，覆盖如下无效取值：
+  a.包含（.）
+  b.包含$
+如：
+db.createRG('test.RG')
+db.createRG('test$RG')
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，删除RG，name为空，如：
+db.removeRG("")
+db.removeRG()
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、RG创建失败，提示参数错误，提示信息合理准确
+2、日志打印信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、RG删除失败，提示参数错误，提示信息合理准确
+2、日志打印信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+语法：
+db.removeRG(&lt;name&gt;)
+删除存在的组</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+语法：
+db.startRG(&lt;name&gt;)
+参数规格：
+name：string，必填
+指定的分区组名必须存在，不然返回异常；如果指定的分区组已经启动，再使用该方法同样会出现异常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、RG重复启动失败，提示组已启动，提示信息合理准确
+2、日志打印信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，startRG,start已启动的组，如：
+db.startRG("group1")，其中group1为启动状态
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，startRG,start不存在的组，如：
+db.startRG("group4")，其中group4不存在
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、RG启动失败，提示组不存在，提示信息合理准确
+2、日志打印信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，startRG,name取值为空串，如：
+db.startRG()
+db.startRG("")
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、RG启动失败，提示参数错误，提示信息合理准确
+2、日志打印信息合理准确</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -251,35 +595,7 @@
   a.不配置config
   b.参见数据库配置一节，配置有效参数   ---参考创建节点config配置（吴艳）  --跟创建节点交叉测试
 2、检查执行结果</t>
-  </si>
-  <si>
-    <t>1、进入sdb，创建CataRG，指定的主机名/IP网络不通，覆盖如下取值：
-  a.无法连接的主机名，如:test（test主机跟处理主机网络不通）
-  b.无法连接的IP，如1.1.1.1（1.1.1.1与处理主机网络不通）
-  c.无效的IP地址，如192.168.*
-如：
-db.createCataRG("1.1.1.1",11800,"/data/11800")
-2、检查执行结果</t>
-  </si>
-  <si>
-    <t>1、进入sdb，创建CataRG，Host取值无效，如：
-db.createCataRG("1.1.*",11800,"/data/11800")
-2、检查执行结果</t>
-  </si>
-  <si>
-    <t>1、进入sdb，创建CataRG，Host取值为空，如：
-db.createCataRG("",11800,"/data/11800")
-db.createCataRG(,11800,"/data/11800")
-2、检查执行结果</t>
-  </si>
-  <si>
-    <t>1、进入sdb，创建CataRG，Service指定的端口被占用，覆盖如下取值：
-  a.指定的端口被占用
-  b.往后顺延的3个端口中其中1个端口被占用
-如：
-db.createCataRG("test",11800,"/data/11800")，其中11800端口被占用
-db.createCataRG("test",11800,"/data/11800")，其中11802端口被占用
-2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>1、进入sdb，创建CataRG，Service无效取值，如：
@@ -289,17 +605,14 @@
 db.createCataRG("test",-1,"/data/11800")
 db.createCataRG("test",65536,"/data/11800")
 2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>1、进入sdb，创建CataRG，Service取值为空，如：
 db.createCataRG("test","","/data/11800")
 db.createCataRG("test",,"/data/11800")
 2、检查执行结果</t>
-  </si>
-  <si>
-    <t>1、sdbadmin用户进入sdb，创建CataRG，Dbpath指定的目录没有写权限，如：
-db.createCataRG("test","11800","/data/11800")，其中/data对sdbadmin没有写权限
-2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>1、进入sdb，创建CataRG，Dbpath无效取值，覆盖如下取值：
@@ -309,18 +622,11 @@
 db.createCataRG("test",11800,"/date/test123@#")
 db.createCataRG("test",11800,"date/11800")
 2、检查执行结果</t>
-  </si>
-  <si>
-    <t>1、进入sdb，创建CataRG，Service取值为空，如：
-db.createCataRG("test",11800,"")
-db.createCataRG("test",11800,)
-2、检查执行结果</t>
-  </si>
-  <si>
-    <t>1、进入sdb，创建CataRG，Service取值为空，如：
-db.createCataRG("test",11800,"/date/11800",[""])
-db.createCataRG("test",11800,"/date/11800",[])
-2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>配置无效的config参数   ---参考创建节点config配置（吴艳）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>1、进入sdb，创建CataRG，参数格式错误，覆盖如下取值：
@@ -331,22 +637,6 @@
 db.testCS.CreateCataRG("testCreateCataRG",{ShardingKey:{"age":1,ShardingType:"hash",Partition:4}) 
 db.testCS.CreateCataRG("testCreateCataRG",{ShardingKey:{"age":1,ShardingType:"range",Partition:1024}) 
 2、检查执行结果</t>
-  </si>
-  <si>
-    <t>1、进入sdb，创建CataRG，参数格式错误，覆盖如下参数格式：
-  a.引号使用错误，如字符串类型不带引号输入、bool类型带引号输入
-  b.多参数
-  c.为空
-如：
-db.createCataRG("test","11800",/date/11800,[config])
-db.createCataRG("test","11800",/date/11800,[config],01)
-db.createCataRG()
-2、检查执行结果</t>
-  </si>
-  <si>
-    <t>1、进入sdb，获取CataRG，如：
-db.getCatalogRG()，其中CM中至少有一个编目组
-2、检查执行结果</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -356,112 +646,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、CM运行正常
-2、CM至少存在一个CataRG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>getCataRG，带条件查询</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、CataRG获取成功，指定的CataRG被直接忽略，返回结果显示所有的CataRG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、CataRG删除成功，指定的CataRG被直接忽略，执行db.listReplicaGroups可以查看到CataRG已被删除
-2、查看CataRG相关配置文件已删除干净</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>listReplicaGroups，带条件查询</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CreateCoordRG，带条件创建</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>语法：
-db.listReplicaGroups()
-无参数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、进入sdb，获取所有CataRG，带条件查询，如：
 db.listReplicaGroups("testCatalogGroup")
 2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、CoordRG获取成功，指定的CoordRG被直接忽略，创建SYSCoord组创建成功，执行db.listReplicaGroups可以查看到已创建的coord组。
-2、在新创建的CoordRG下创建节点，节点创建成功，且可用正常启停，节点可正常连接</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>语法：
-db.createCoordRG()
-无参数</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>语法：
-db.removeCoordRG()，无参数
-删除协调分区组，原则上会把该分区组的所有协调节点都删除</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>removeCoordRG()，删除为空和不为空的组</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，创建CoordRG，带条件查询，如：
-db.createCoordRG("testCoordRG")
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，删除CoordRG，覆盖如下取值：
-   a.CoordRG为空
-   b.CoordRG有至少一个Coord节点，组不为空
-执行removeCoordRG()
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、CoordRG删除成功，组下的节点也一并删除，执行db.listReplicaGroups可以查看到CoordRG已被删除
-2、查看CoordRG相关配置文件已删除干净</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，带条件查询，如：
-db.getCatalogRG("testCatalogGroup")
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>removeCoordRG()，带条件删除</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，带条件删除，如：
-db.removeCoordRG("testCoordRG")
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、CoordRG删除成功，指定的CoordRG被直接忽略，执行db.listReplicaGroups可以查看到CoordRG已被删除
-2、查看CoordRG相关配置文件已删除干净</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>语法：
 db.createRG(&lt;name&gt;)
 string,必填，同一个数据库对象中，分区组名唯一。name不能是空串，含点（.）或者美元符号（$），并且长度不能超过127B。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createRG，覆盖name有效字符和边界</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -473,120 +666,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>removeRG，删除不存在的组</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、CM运行正常
-2、CM至少存在一个RG</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，删除不存在的RG，如：
-db.removeRG("test")，其中test组不存在
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、RG删除失败，提示test组不存在，执行db.listReplicaGroups其他已存在的RG不会被删除
-2、日志打印信息合理正确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createRG，name字符无效</t>
-  </si>
-  <si>
-    <t>createRG，name长度无效</t>
-  </si>
-  <si>
-    <t>createRG，name重复</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">1、首次创建name唯一RG，创建成功
-2、重复创建相同name的RG，创建失败，返回结果报错，并提示RG名已存在，提示信息合理准确
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、CataRG创建成功，执行db.listReplicaGroups可以查看到新创建的CataRG。
-检查Config默认取值正确。
-2、在新创建的CataRG下创建节点，节点创建成功，且可用正常启停；创建CS、RG并插入数据，数据插入成功。</t>
-  </si>
-  <si>
-    <t>1、RG创建成功，执行db.listReplicaGroups可以查看到新创建的RG。
-2、在新创建的CataRG下创建节点，节点创建成功，且可用正常启停；创建CS、RG并插入数据，数据插入成功。
-切分数据，数据可以切分成功；同步数据，数据可以同步成功；</t>
-  </si>
-  <si>
-    <t>1、进入sdb，创建RG，输入有效的name创建RG，如：
-db.createRG("testRG")
-2、重复步骤1，创建name相同的RG
-3、检查执行结果</t>
-  </si>
-  <si>
-    <t>1、RG创建失败，提示参数不合法，提示信息合理准确
-2、日志打印信息合理准确</t>
-  </si>
-  <si>
-    <t>1、RG创建失败，提示参数超出长度，提示信息合理准确
-2、日志打印信息合理准确</t>
-  </si>
-  <si>
-    <t>1、进入sdb，创建RG，输入name长度无效，覆盖如下无效取值：
-  a.空串
-  b.128字节
-如：
-db.createRG('')  或  db.createRG()   或  为128字节的有效字符
-3、检查执行结果</t>
-  </si>
-  <si>
-    <t>createRG，格式错误</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，创建RG，格式错误，如：
-db.createRG()
-db.createRG("testRG","testRG2",123)
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>removeRG，name为空</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，创建RG，输入name字符无效，覆盖如下无效取值：
-  a.包含（.）
-  b.包含$
-如：
-db.createRG('test.RG')
-db.createRG('test$RG')
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，删除RG，name为空，如：
-db.removeRG("")
-db.removeRG()
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、RG创建失败，提示参数错误，提示信息合理准确
-2、日志打印信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、RG删除失败，提示参数错误，提示信息合理准确
-2、日志打印信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>removeRG，格式错误</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、进入sdb，删除RG，格式错误，如：
 db.removeRG()
 db.removeRG("testRG","testRG2",123)
@@ -594,73 +673,128 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">
-语法：
-db.removeRG(&lt;name&gt;)
-删除存在的组</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">
-语法：
-db.startRG(&lt;name&gt;)
+    <t>语法：db.createCataRG(&lt;host&gt;,&lt;service&gt;,&lt;dbpath&gt;,[config])
+格式：{"&lt;主机名/主机IP&gt;",&lt;端口号&gt;,"&lt;数据文件路径&gt;",[数据库配置参数对象]}
 参数规格：
-name：string，必填
-指定的分区组名必须存在，不然返回异常；如果指定的分区组已经启动，再使用该方法同样会出现异常</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>startRG,name取值为空串</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>startRG,start已启动的组</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>startRG,start不存在的组</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、RG重复启动失败，提示组已启动，提示信息合理准确
-2、日志打印信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，startRG,start已启动的组，如：
-db.startRG("group1")，其中group1为启动状态
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，startRG,start不存在的组，如：
-db.startRG("group4")，其中group4不存在
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、RG启动失败，提示组不存在，提示信息合理准确
-2、日志打印信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、进入sdb，startRG,name取值为空串，如：
-db.startRG()
-db.startRG("")
-2、检查执行结果</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、RG启动失败，提示参数错误，提示信息合理准确
-2、日志打印信息合理准确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+Host：string，必填,主机通信正常
+Service：int，必填，端口不被占用，包括往后顺延的3个端口。端口取值范围（0~65535）
+Dbpath：string，必填，需确保数据管理员（安装时创建，默认为 sdbadmin）用户有写权限。
+路径不存在会自动创建
+Config：Json对象，非必填
+参见数据库配置一节</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CreateCataRG，覆盖Host/Service/Dbpath有效字符和边界_st.verify.groupMrg.001</t>
+  </si>
+  <si>
+    <t>CreateCataRG，Host指定的主机名/IP网络不通_st.verify.groupMrg.002</t>
+  </si>
+  <si>
+    <t>CreateCataRG，Host取值无效_st.verify.groupMrg.003</t>
+  </si>
+  <si>
+    <t>CreateCataRG，Host取值为空_st.verify.groupMrg.004</t>
+  </si>
+  <si>
+    <t>CreateCataRG，Service指定的端口被占用_st.verify.groupMrg.005</t>
+  </si>
+  <si>
+    <t>CreateCataRG，Service无效取值_st.verify.groupMrg.006</t>
+  </si>
+  <si>
+    <t>CreateCataRG，Service取值为空_st.verify.groupMrg.007</t>
+  </si>
+  <si>
+    <t>CreateCataRG，Dbpath指定的目录没有写权限_st.verify.groupMrg.008</t>
+  </si>
+  <si>
+    <t>CreateCataRG，Dbpath无效取值_st.verify.groupMrg.009</t>
+  </si>
+  <si>
+    <t>CreateCataRG，Dbpath取值为空_st.verify.groupMrg.010</t>
+  </si>
+  <si>
+    <t>CreateCataRG，Config无效取值_st.verify.groupMrg.011</t>
+  </si>
+  <si>
+    <t>CreateCataRG，Config取值为空_st.verify.groupMrg.012</t>
+  </si>
+  <si>
+    <t>CreateCataRG，参数格式错误_st.verify.groupMrg.013</t>
+  </si>
+  <si>
+    <t>CreateCataRG，格式错误_st.verify.groupMrg.014</t>
+  </si>
+  <si>
+    <t>removeCataRG，删除为空的CataRG_st.verify.groupMrg.015</t>
+  </si>
+  <si>
+    <t>removeCataRG，删除的CataRG包含数据节点信息_st.verify.groupMrg.016</t>
+  </si>
+  <si>
+    <t>removeCataRG，删除的CataRG包含协调节点信息_st.verify.groupMrg.017</t>
+  </si>
+  <si>
+    <t>removeCataRG，带条件删除_st.verify.groupMrg.018</t>
+  </si>
+  <si>
+    <t>getCataRG，获取存在的组_st.verify.groupMrg.019</t>
+  </si>
+  <si>
+    <t>getCataRG，带条件查询_st.verify.groupMrg.020</t>
+  </si>
+  <si>
+    <t>listReplicaGroups，带条件查询_st.verify.groupMrg.021</t>
+  </si>
+  <si>
+    <t>CreateCoordRG，带条件创建_st.verify.groupMrg.022</t>
+  </si>
+  <si>
+    <t>removeCoordRG()，删除为空和不为空的组_st.verify.groupMrg.023</t>
+  </si>
+  <si>
+    <t>removeCoordRG()，带条件删除_st.verify.groupMrg.024</t>
+  </si>
+  <si>
+    <t>createRG，覆盖name有效字符和边界_st.verify.groupMrg.025</t>
+  </si>
+  <si>
+    <t>createRG，name重复_st.verify.groupMrg.026</t>
+  </si>
+  <si>
+    <t>createRG，name字符无效_st.verify.groupMrg.027</t>
+  </si>
+  <si>
+    <t>createRG，name长度无效_st.verify.groupMrg.028</t>
+  </si>
+  <si>
+    <t>createRG，格式错误_st.verify.groupMrg.029</t>
+  </si>
+  <si>
+    <t>removeRG，删除不存在的组_st.verify.groupMrg.030</t>
+  </si>
+  <si>
+    <t>removeRG，name为空_st.verify.groupMrg.031</t>
+  </si>
+  <si>
+    <t>removeRG，格式错误_st.verify.groupMrg.032</t>
+  </si>
+  <si>
+    <t>startRG,start已启动的组_st.verify.groupMrg.033</t>
+  </si>
+  <si>
+    <t>startRG,start不存在的组_st.verify.groupMrg.034</t>
+  </si>
+  <si>
+    <t>startRG,name取值为空串_st.verify.groupMrg.035</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -689,6 +823,34 @@
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1219,28 +1381,28 @@
     </row>
     <row r="3" spans="1:9" ht="174" customHeight="1">
       <c r="A3" s="2" t="s">
-        <v>21</v>
+        <v>87</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>19</v>
+        <v>86</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D3" s="4">
         <v>1</v>
       </c>
       <c r="E3" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" s="4">
         <v>1</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="I3" s="4">
         <v>1</v>
@@ -1248,641 +1410,923 @@
     </row>
     <row r="4" spans="1:9" ht="148.5">
       <c r="A4" s="2" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="4">
+        <v>1</v>
+      </c>
+      <c r="E4" s="4">
+        <v>2</v>
+      </c>
+      <c r="F4" s="4">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="H4" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="4">
-        <v>1</v>
-      </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="I4" s="4"/>
+      <c r="I4" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:9" ht="54">
       <c r="A5" s="2" t="s">
-        <v>24</v>
+        <v>89</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D5" s="4">
+        <v>1</v>
+      </c>
+      <c r="E5" s="4">
+        <v>2</v>
+      </c>
+      <c r="F5" s="4">
+        <v>1</v>
+      </c>
       <c r="G5" s="2" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I5" s="4"/>
+        <v>21</v>
+      </c>
+      <c r="I5" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:9" ht="54">
       <c r="A6" s="2" t="s">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D6" s="4">
+        <v>1</v>
+      </c>
+      <c r="E6" s="4">
+        <v>2</v>
+      </c>
+      <c r="F6" s="4">
+        <v>1</v>
+      </c>
       <c r="G6" s="2" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I6" s="4"/>
+        <v>21</v>
+      </c>
+      <c r="I6" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:9" ht="135">
       <c r="A7" s="2" t="s">
-        <v>26</v>
+        <v>91</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D7" s="4">
+        <v>1</v>
+      </c>
+      <c r="E7" s="4">
+        <v>2</v>
+      </c>
+      <c r="F7" s="4">
+        <v>1</v>
+      </c>
       <c r="G7" s="2" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I7" s="4"/>
+        <v>22</v>
+      </c>
+      <c r="I7" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:9" ht="108">
       <c r="A8" s="2" t="s">
-        <v>27</v>
+        <v>92</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D8" s="4">
         <v>1</v>
       </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
+      <c r="E8" s="4">
+        <v>2</v>
+      </c>
+      <c r="F8" s="4">
+        <v>1</v>
+      </c>
       <c r="G8" s="2" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I8" s="4"/>
+        <v>21</v>
+      </c>
+      <c r="I8" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:9" ht="54">
       <c r="A9" s="2" t="s">
-        <v>25</v>
+        <v>93</v>
       </c>
       <c r="B9" s="7"/>
       <c r="C9" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D9" s="4">
         <v>1</v>
       </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4"/>
+      <c r="E9" s="4">
+        <v>2</v>
+      </c>
+      <c r="F9" s="4">
+        <v>1</v>
+      </c>
       <c r="G9" s="2" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I9" s="4"/>
+        <v>21</v>
+      </c>
+      <c r="I9" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:9" ht="67.5">
       <c r="A10" s="2" t="s">
-        <v>28</v>
+        <v>94</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D10" s="4">
         <v>1</v>
       </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
+      <c r="E10" s="4">
+        <v>2</v>
+      </c>
+      <c r="F10" s="4">
+        <v>1</v>
+      </c>
       <c r="G10" s="2" t="s">
-        <v>58</v>
+        <v>34</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="I10" s="4"/>
+        <v>23</v>
+      </c>
+      <c r="I10" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:9" ht="121.5">
       <c r="A11" s="2" t="s">
-        <v>29</v>
+        <v>95</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D11" s="4">
         <v>1</v>
       </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4"/>
+      <c r="E11" s="4">
+        <v>2</v>
+      </c>
+      <c r="F11" s="4">
+        <v>1</v>
+      </c>
       <c r="G11" s="2" t="s">
-        <v>59</v>
+        <v>78</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I11" s="4"/>
+        <v>21</v>
+      </c>
+      <c r="I11" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:9" ht="54">
       <c r="A12" s="2" t="s">
-        <v>30</v>
+        <v>96</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D12" s="4">
+        <v>1</v>
+      </c>
+      <c r="E12" s="4">
+        <v>2</v>
+      </c>
+      <c r="F12" s="4">
+        <v>1</v>
+      </c>
       <c r="G12" s="2" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I12" s="4"/>
+        <v>21</v>
+      </c>
+      <c r="I12" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:9" ht="40.5">
       <c r="A13" s="2" t="s">
-        <v>31</v>
+        <v>97</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D13" s="4">
         <v>1</v>
       </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4"/>
+      <c r="E13" s="4">
+        <v>2</v>
+      </c>
+      <c r="F13" s="4">
+        <v>1</v>
+      </c>
       <c r="G13" s="8" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I13" s="4"/>
+        <v>21</v>
+      </c>
+      <c r="I13" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:9" ht="81">
       <c r="A14" s="2" t="s">
-        <v>33</v>
+        <v>98</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D14" s="4">
+        <v>1</v>
+      </c>
+      <c r="E14" s="4">
+        <v>2</v>
+      </c>
+      <c r="F14" s="4">
+        <v>1</v>
+      </c>
       <c r="G14" s="2" t="s">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I14" s="4"/>
+        <v>21</v>
+      </c>
+      <c r="I14" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:9" ht="189">
       <c r="A15" s="2" t="s">
-        <v>34</v>
+        <v>99</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D15" s="4">
         <v>1</v>
       </c>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4"/>
+      <c r="E15" s="4">
+        <v>2</v>
+      </c>
+      <c r="F15" s="4">
+        <v>1</v>
+      </c>
       <c r="G15" s="2" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I15" s="4"/>
+        <v>21</v>
+      </c>
+      <c r="I15" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:9" ht="175.5">
       <c r="A16" s="2" t="s">
-        <v>18</v>
+        <v>100</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D16" s="4">
         <v>1</v>
       </c>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
+      <c r="E16" s="4">
+        <v>2</v>
+      </c>
+      <c r="F16" s="4">
+        <v>1</v>
+      </c>
       <c r="G16" s="2" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I16" s="4"/>
+        <v>21</v>
+      </c>
+      <c r="I16" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" spans="1:9" ht="81">
       <c r="A17" s="2" t="s">
-        <v>35</v>
+        <v>101</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>65</v>
+        <v>81</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="D17" s="4">
         <v>1</v>
       </c>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4"/>
+      <c r="E17" s="4">
+        <v>1</v>
+      </c>
+      <c r="F17" s="4">
+        <v>1</v>
+      </c>
       <c r="G17" s="2" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="I17" s="4"/>
+        <v>26</v>
+      </c>
+      <c r="I17" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="18" spans="1:9" ht="54">
       <c r="A18" s="2" t="s">
-        <v>41</v>
+        <v>102</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="1" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="D18" s="4">
         <v>1</v>
       </c>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4"/>
+      <c r="E18" s="4">
+        <v>2</v>
+      </c>
+      <c r="F18" s="4">
+        <v>1</v>
+      </c>
       <c r="G18" s="2" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="I18" s="4"/>
+        <v>28</v>
+      </c>
+      <c r="I18" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="19" spans="1:9" ht="54">
       <c r="A19" s="2" t="s">
-        <v>42</v>
+        <v>103</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="D19" s="4"/>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4"/>
+        <v>39</v>
+      </c>
+      <c r="D19" s="4">
+        <v>1</v>
+      </c>
+      <c r="E19" s="4">
+        <v>2</v>
+      </c>
+      <c r="F19" s="4">
+        <v>1</v>
+      </c>
       <c r="G19" s="2" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="I19" s="4"/>
+        <v>28</v>
+      </c>
+      <c r="I19" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" spans="1:9" ht="54">
       <c r="A20" s="2" t="s">
-        <v>45</v>
+        <v>104</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="D20" s="4">
         <v>1</v>
       </c>
+      <c r="E20" s="4">
+        <v>1</v>
+      </c>
+      <c r="F20" s="4">
+        <v>1</v>
+      </c>
       <c r="G20" s="2" t="s">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>69</v>
+        <v>41</v>
+      </c>
+      <c r="I20" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:9" ht="54">
       <c r="A21" s="2" t="s">
-        <v>50</v>
+        <v>105</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="D21" s="4">
         <v>1</v>
       </c>
+      <c r="E21" s="4">
+        <v>2</v>
+      </c>
+      <c r="F21" s="4">
+        <v>1</v>
+      </c>
       <c r="G21" s="2" t="s">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>38</v>
+        <v>21</v>
+      </c>
+      <c r="I21" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="40.5">
       <c r="A22" s="2" t="s">
-        <v>67</v>
+        <v>106</v>
       </c>
       <c r="B22" s="6"/>
       <c r="C22" s="1" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="D22" s="4">
         <v>1</v>
       </c>
+      <c r="E22" s="4">
+        <v>1</v>
+      </c>
+      <c r="F22" s="4">
+        <v>1</v>
+      </c>
       <c r="G22" s="2" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>68</v>
+        <v>40</v>
+      </c>
+      <c r="I22" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:9" ht="40.5">
       <c r="A23" s="2" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D23" s="4">
         <v>1</v>
       </c>
+      <c r="E23" s="4">
+        <v>1</v>
+      </c>
+      <c r="F23" s="4">
+        <v>1</v>
+      </c>
       <c r="G23" s="2" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>68</v>
+        <v>40</v>
+      </c>
+      <c r="I23" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:9" ht="94.5">
       <c r="A24" s="2" t="s">
-        <v>71</v>
+        <v>108</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>75</v>
+        <v>44</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D24" s="4"/>
-      <c r="E24" s="4"/>
-      <c r="F24" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="D24" s="4">
+        <v>1</v>
+      </c>
+      <c r="E24" s="4">
+        <v>1</v>
+      </c>
+      <c r="F24" s="4">
+        <v>1</v>
+      </c>
       <c r="G24" s="2" t="s">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="I24" s="4"/>
+        <v>43</v>
+      </c>
+      <c r="I24" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="25" spans="1:9" ht="67.5">
       <c r="A25" s="2" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>76</v>
+        <v>45</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
+      </c>
+      <c r="D25" s="4">
+        <v>1</v>
+      </c>
+      <c r="E25" s="4">
+        <v>1</v>
+      </c>
+      <c r="F25" s="4">
+        <v>1</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>79</v>
+        <v>47</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>80</v>
+        <v>48</v>
+      </c>
+      <c r="I25" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:9" ht="81">
       <c r="A26" s="2" t="s">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="D26" s="4">
         <v>1</v>
       </c>
+      <c r="E26" s="4">
+        <v>1</v>
+      </c>
+      <c r="F26" s="4">
+        <v>1</v>
+      </c>
       <c r="G26" s="2" t="s">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>84</v>
+        <v>51</v>
+      </c>
+      <c r="I26" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:9" ht="121.5">
       <c r="A27" s="2" t="s">
-        <v>86</v>
+        <v>111</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
+      </c>
+      <c r="D27" s="4">
+        <v>1</v>
+      </c>
+      <c r="E27" s="4">
+        <v>1</v>
+      </c>
+      <c r="F27" s="4">
+        <v>1</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>97</v>
+        <v>57</v>
+      </c>
+      <c r="I27" s="4">
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:9" ht="67.5">
       <c r="A28" s="2" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D28" s="4">
         <v>1</v>
       </c>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
+      <c r="E28" s="4">
+        <v>1</v>
+      </c>
+      <c r="F28" s="4">
+        <v>1</v>
+      </c>
       <c r="G28" s="2" t="s">
-        <v>98</v>
+        <v>58</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="I28" s="4"/>
+        <v>55</v>
+      </c>
+      <c r="I28" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" spans="1:9" ht="108">
       <c r="A29" s="2" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D29" s="4">
         <v>1</v>
       </c>
-      <c r="E29" s="4"/>
-      <c r="F29" s="4"/>
+      <c r="E29" s="4">
+        <v>2</v>
+      </c>
+      <c r="F29" s="4">
+        <v>1</v>
+      </c>
       <c r="G29" s="2" t="s">
-        <v>105</v>
+        <v>63</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="I29" s="4"/>
+        <v>59</v>
+      </c>
+      <c r="I29" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="1:9" ht="108">
       <c r="A30" s="2" t="s">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="B30" s="7"/>
       <c r="C30" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D30" s="4">
         <v>1</v>
       </c>
-      <c r="E30" s="4"/>
-      <c r="F30" s="4"/>
+      <c r="E30" s="4">
+        <v>2</v>
+      </c>
+      <c r="F30" s="4">
+        <v>1</v>
+      </c>
       <c r="G30" s="2" t="s">
-        <v>101</v>
+        <v>61</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="I30" s="4"/>
+        <v>60</v>
+      </c>
+      <c r="I30" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" spans="1:9" ht="54">
       <c r="A31" s="2" t="s">
-        <v>102</v>
+        <v>115</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D31" s="4">
         <v>1</v>
       </c>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
+      <c r="E31" s="4">
+        <v>2</v>
+      </c>
+      <c r="F31" s="4">
+        <v>1</v>
+      </c>
       <c r="G31" s="2" t="s">
-        <v>103</v>
+        <v>62</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="I31" s="4"/>
+        <v>65</v>
+      </c>
+      <c r="I31" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="32" spans="1:9" ht="67.5">
       <c r="A32" s="1" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>111</v>
+        <v>67</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>89</v>
+        <v>52</v>
+      </c>
+      <c r="D32" s="4">
+        <v>1</v>
+      </c>
+      <c r="E32" s="4">
+        <v>2</v>
+      </c>
+      <c r="F32" s="4">
+        <v>1</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="54">
+        <v>54</v>
+      </c>
+      <c r="I32" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="54">
       <c r="A33" s="1" t="s">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
+      </c>
+      <c r="D33" s="4">
+        <v>1</v>
+      </c>
+      <c r="E33" s="4">
+        <v>2</v>
+      </c>
+      <c r="F33" s="4">
+        <v>1</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>106</v>
+        <v>64</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="54">
+        <v>66</v>
+      </c>
+      <c r="I33" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="54">
       <c r="A34" s="1" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
+      </c>
+      <c r="D34" s="4">
+        <v>1</v>
+      </c>
+      <c r="E34" s="4">
+        <v>2</v>
+      </c>
+      <c r="F34" s="4">
+        <v>1</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="121.5">
+        <v>66</v>
+      </c>
+      <c r="I34" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="121.5">
       <c r="A35" s="1" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>112</v>
+        <v>68</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
+      </c>
+      <c r="D35" s="4">
+        <v>1</v>
+      </c>
+      <c r="E35" s="4">
+        <v>2</v>
+      </c>
+      <c r="F35" s="4">
+        <v>1</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>117</v>
+        <v>70</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="40.5">
+        <v>69</v>
+      </c>
+      <c r="I35" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="40.5">
       <c r="A36" s="1" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
+      </c>
+      <c r="D36" s="4">
+        <v>1</v>
+      </c>
+      <c r="E36" s="4">
+        <v>2</v>
+      </c>
+      <c r="F36" s="4">
+        <v>1</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>118</v>
+        <v>71</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="54">
+        <v>72</v>
+      </c>
+      <c r="I36" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="54">
       <c r="A37" s="1" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
+      </c>
+      <c r="D37" s="4">
+        <v>1</v>
+      </c>
+      <c r="E37" s="4">
+        <v>2</v>
+      </c>
+      <c r="F37" s="4">
+        <v>1</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>120</v>
+        <v>73</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>121</v>
+        <v>74</v>
+      </c>
+      <c r="I37" s="4">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
--- a/internal_doc/05.测试设计/参数校验/测试用例/集群管理（组管理）参数校验测试用例.xlsx
+++ b/internal_doc/05.测试设计/参数校验/测试用例/集群管理（组管理）参数校验测试用例.xlsx
@@ -144,7 +144,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A34" authorId="0">
+    <comment ref="A35" authorId="0">
       <text>
         <r>
           <rPr>
@@ -183,7 +183,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="153">
   <si>
     <t>name</t>
   </si>
@@ -755,39 +755,210 @@
   </si>
   <si>
     <t>removeCoordRG()，带条件删除_st.verify.groupMrg.024</t>
-  </si>
-  <si>
-    <t>createRG，覆盖name有效字符和边界_st.verify.groupMrg.025</t>
-  </si>
-  <si>
-    <t>createRG，name重复_st.verify.groupMrg.026</t>
-  </si>
-  <si>
-    <t>createRG，name字符无效_st.verify.groupMrg.027</t>
-  </si>
-  <si>
-    <t>createRG，name长度无效_st.verify.groupMrg.028</t>
-  </si>
-  <si>
-    <t>createRG，格式错误_st.verify.groupMrg.029</t>
-  </si>
-  <si>
-    <t>removeRG，删除不存在的组_st.verify.groupMrg.030</t>
-  </si>
-  <si>
-    <t>removeRG，name为空_st.verify.groupMrg.031</t>
-  </si>
-  <si>
-    <t>removeRG，格式错误_st.verify.groupMrg.032</t>
-  </si>
-  <si>
-    <t>startRG,start已启动的组_st.verify.groupMrg.033</t>
-  </si>
-  <si>
-    <t>startRG,start不存在的组_st.verify.groupMrg.034</t>
-  </si>
-  <si>
-    <t>startRG,name取值为空串_st.verify.groupMrg.035</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，带条件查询，如：
+db.getCoordRG("testCoordRG")
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、CoordRG获取成功，指定的CoordRG被直接忽略，返回结果显示所有的CoordRG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+语法：
+db.startRG(&lt;name&gt;)
+参数规格：
+name：string，name 和 id 任选
+分区组名。同一个数据库对象中，分区组名唯一。
+id：int，分区组 id，创建分区组时系统自动分配。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，getRG，name指定的RG存在，如：
+db.getRG("rg1")，其中rg在sdb存在
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、指定的RG获取成功，返回结果指显示该指定的RG，数据显示合理正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，getRG，name指定的RG不存在，如：
+db.getRG("rg1")，其中rg在sdb不存在
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取失败，提示RG不存在，提示信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，getRG，name指定的RG存在，如：
+db.getRG(1000)，其中1000在sdb存在
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，getRG，name指定的RG不存在，如：
+db.getRG(1111)，其中1111在sdb不存在
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，getRG，name和id同时指定RG查询，如：
+db.getRG("rg1",1000)，其中rg在sdb存在
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>获取失败，提示参数错误，提示信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，getRG，取值为空，如：
+db.getRG("")
+db.getRG()
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>getCoordRG，带条件查询_st.verify.groupMrg.025</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createRG，覆盖name有效字符和边界_st.verify.groupMrg.026</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createRG，name重复_st.verify.groupMrg.027</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createRG，name字符无效_st.verify.groupMrg.028</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createRG，name长度无效_st.verify.groupMrg.029</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createRG，格式错误_st.verify.groupMrg.030</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>removeRG，删除不存在的组_st.verify.groupMrg.031</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>removeRG，name为空_st.verify.groupMrg.032</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>removeRG，格式错误_st.verify.groupMrg.033</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>getRG，name指定的RG存在_st.verify.groupMrg.034</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>getRG，name指定的RG不存在_st.verify.groupMrg.035</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>getRG，id指定的RG存在_st.verify.groupMrg.036</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>getRG，id指定的RG不存在_st.verify.groupMrg.037</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>getRG，name和id同时指定RG查询_st.verify.groupMrg.038</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>getRG，取值为空_st.verify.groupMrg.039</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>startRG,start已启动的组_st.verify.groupMrg.040</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>startRG,start不存在的组_st.verify.groupMrg.041</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>startRG,name取值为空串_st.verify.groupMrg.042</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CreateSpareRG，带条件创建_st.verify.groupMrg.043</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>removeSpareRG，带条件删除_st.verify.groupMrg.044</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>getSpareRG，带条件查询_st.verify.groupMrg.045</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，创建CoordRG，带条件查询，如：
+db.createSpareRG("testSpareRG")
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，带条件删除，如：
+db.removeSpareRG("SYSSpareGroup")
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、进入sdb，带条件查询，如：
+db.getSpareRG("testSpareGroup")
+2、检查执行结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、SpareRG创建成功，指定的SpareRG被直接忽略，创建SYSSpare组创建成功，执行db.listReplicaGroups可以查看到已创建的coord组。
+2、在新创建的SpareRG下创建节点，节点创建成功，且可用正常启停，节点可正常连接</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、SpareRG删除成功，指定的SpareRG被直接忽略，执行db.listReplicaGroups可以查看到SpareRG已被删除
+2、查看SpareRG相关配置文件已删除干净</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、SpareRG获取成功，指定的SpareRG被直接忽略，返回结果显示所有的SpareRG</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语法：
+db.createSpareRG()
+无参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语法：
+db.removeSpareRG()
+无参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>语法：
+db.getSpareRG()
+无参数</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -988,8 +1159,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I37" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
-  <autoFilter ref="A1:I37"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I47" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
+  <autoFilter ref="A1:I47"/>
   <tableColumns count="9">
     <tableColumn id="1" uniqueName="name" name="name" dataDxfId="8">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/@name" xmlDataType="string"/>
@@ -1308,7 +1479,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I37"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="26.375" style="1" customWidth="1"/>
@@ -2024,38 +2195,39 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:9" ht="121.5">
+    <row r="27" spans="1:9" ht="40.5">
       <c r="A27" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="B27" s="6"/>
+      <c r="C27" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D27" s="4">
+        <v>1</v>
+      </c>
+      <c r="E27" s="4">
+        <v>1</v>
+      </c>
+      <c r="F27" s="4">
+        <v>1</v>
+      </c>
+      <c r="G27" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="H27" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="I27" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="121.5">
+      <c r="A28" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B28" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D27" s="4">
-        <v>1</v>
-      </c>
-      <c r="E27" s="4">
-        <v>1</v>
-      </c>
-      <c r="F27" s="4">
-        <v>1</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="I27" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" ht="67.5">
-      <c r="A28" s="2" t="s">
-        <v>112</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>18</v>
@@ -2070,18 +2242,18 @@
         <v>1</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="I28" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="108">
+    <row r="29" spans="1:9" ht="67.5">
       <c r="A29" s="2" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>18</v>
@@ -2090,16 +2262,16 @@
         <v>1</v>
       </c>
       <c r="E29" s="4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F29" s="4">
         <v>1</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="I29" s="4">
         <v>1</v>
@@ -2107,9 +2279,8 @@
     </row>
     <row r="30" spans="1:9" ht="108">
       <c r="A30" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B30" s="7"/>
+        <v>126</v>
+      </c>
       <c r="C30" s="1" t="s">
         <v>18</v>
       </c>
@@ -2123,19 +2294,20 @@
         <v>1</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="I30" s="4">
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:9" ht="54">
+    <row r="31" spans="1:9" ht="108">
       <c r="A31" s="2" t="s">
-        <v>115</v>
-      </c>
+        <v>127</v>
+      </c>
+      <c r="B31" s="7"/>
       <c r="C31" s="1" t="s">
         <v>18</v>
       </c>
@@ -2149,65 +2321,65 @@
         <v>1</v>
       </c>
       <c r="G31" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I31" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" ht="54">
+      <c r="A32" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D32" s="4">
+        <v>1</v>
+      </c>
+      <c r="E32" s="4">
+        <v>2</v>
+      </c>
+      <c r="F32" s="4">
+        <v>1</v>
+      </c>
+      <c r="G32" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="H31" s="2" t="s">
+      <c r="H32" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="I31" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" ht="67.5">
-      <c r="A32" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="B32" s="5" t="s">
+      <c r="I32" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="67.5">
+      <c r="A33" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B33" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C33" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D32" s="4">
-        <v>1</v>
-      </c>
-      <c r="E32" s="4">
-        <v>2</v>
-      </c>
-      <c r="F32" s="4">
-        <v>1</v>
-      </c>
-      <c r="G32" s="2" t="s">
+      <c r="D33" s="4">
+        <v>1</v>
+      </c>
+      <c r="E33" s="4">
+        <v>2</v>
+      </c>
+      <c r="F33" s="4">
+        <v>1</v>
+      </c>
+      <c r="G33" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="H32" s="2" t="s">
+      <c r="H33" s="2" t="s">
         <v>54</v>
-      </c>
-      <c r="I32" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" ht="54">
-      <c r="A33" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D33" s="4">
-        <v>1</v>
-      </c>
-      <c r="E33" s="4">
-        <v>2</v>
-      </c>
-      <c r="F33" s="4">
-        <v>1</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>66</v>
       </c>
       <c r="I33" s="4">
         <v>1</v>
@@ -2215,7 +2387,7 @@
     </row>
     <row r="34" spans="1:9" ht="54">
       <c r="A34" s="1" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>18</v>
@@ -2230,7 +2402,7 @@
         <v>1</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>85</v>
+        <v>64</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>66</v>
@@ -2239,12 +2411,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:9" ht="121.5">
+    <row r="35" spans="1:9" ht="54">
       <c r="A35" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>68</v>
+        <v>131</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>18</v>
@@ -2259,64 +2428,331 @@
         <v>1</v>
       </c>
       <c r="G35" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="I35" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="148.5">
+      <c r="A36" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D36" s="4">
+        <v>1</v>
+      </c>
+      <c r="E36" s="4">
+        <v>1</v>
+      </c>
+      <c r="F36" s="4">
+        <v>1</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I36" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="40.5">
+      <c r="A37" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D37" s="4">
+        <v>1</v>
+      </c>
+      <c r="E37" s="4">
+        <v>2</v>
+      </c>
+      <c r="F37" s="4">
+        <v>1</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I37" s="4"/>
+    </row>
+    <row r="38" spans="1:9" ht="40.5">
+      <c r="A38" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D38" s="4">
+        <v>1</v>
+      </c>
+      <c r="E38" s="4">
+        <v>1</v>
+      </c>
+      <c r="F38" s="4">
+        <v>1</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="I38" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="40.5">
+      <c r="A39" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D39" s="4">
+        <v>1</v>
+      </c>
+      <c r="E39" s="4">
+        <v>2</v>
+      </c>
+      <c r="F39" s="4">
+        <v>1</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I39" s="4"/>
+    </row>
+    <row r="40" spans="1:9" ht="54">
+      <c r="A40" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D40" s="4">
+        <v>1</v>
+      </c>
+      <c r="E40" s="4">
+        <v>1</v>
+      </c>
+      <c r="F40" s="4">
+        <v>1</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="I40" s="4"/>
+    </row>
+    <row r="41" spans="1:9" ht="54">
+      <c r="A41" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D41" s="4">
+        <v>1</v>
+      </c>
+      <c r="E41" s="4">
+        <v>2</v>
+      </c>
+      <c r="F41" s="4">
+        <v>1</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="I41" s="4"/>
+    </row>
+    <row r="42" spans="1:9" ht="121.5">
+      <c r="A42" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D42" s="4">
+        <v>1</v>
+      </c>
+      <c r="E42" s="4">
+        <v>2</v>
+      </c>
+      <c r="F42" s="4">
+        <v>1</v>
+      </c>
+      <c r="G42" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="H35" s="2" t="s">
+      <c r="H42" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="I35" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" ht="40.5">
-      <c r="A36" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C36" s="1" t="s">
+      <c r="I42" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="40.5">
+      <c r="A43" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="C43" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D36" s="4">
-        <v>1</v>
-      </c>
-      <c r="E36" s="4">
-        <v>2</v>
-      </c>
-      <c r="F36" s="4">
-        <v>1</v>
-      </c>
-      <c r="G36" s="2" t="s">
+      <c r="D43" s="4">
+        <v>1</v>
+      </c>
+      <c r="E43" s="4">
+        <v>2</v>
+      </c>
+      <c r="F43" s="4">
+        <v>1</v>
+      </c>
+      <c r="G43" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="H36" s="2" t="s">
+      <c r="H43" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="I36" s="4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" ht="54">
-      <c r="A37" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="C37" s="1" t="s">
+      <c r="I43" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="54">
+      <c r="A44" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C44" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D37" s="4">
-        <v>1</v>
-      </c>
-      <c r="E37" s="4">
-        <v>2</v>
-      </c>
-      <c r="F37" s="4">
-        <v>1</v>
-      </c>
-      <c r="G37" s="2" t="s">
+      <c r="D44" s="4">
+        <v>1</v>
+      </c>
+      <c r="E44" s="4">
+        <v>2</v>
+      </c>
+      <c r="F44" s="4">
+        <v>1</v>
+      </c>
+      <c r="G44" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="H37" s="2" t="s">
+      <c r="H44" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="I37" s="4">
+      <c r="I44" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" ht="94.5">
+      <c r="A45" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D45" s="4">
+        <v>1</v>
+      </c>
+      <c r="E45" s="4">
+        <v>1</v>
+      </c>
+      <c r="F45" s="4">
+        <v>1</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="I45" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="81">
+      <c r="A46" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B46" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D46" s="4">
+        <v>1</v>
+      </c>
+      <c r="E46" s="4">
+        <v>1</v>
+      </c>
+      <c r="F46" s="4">
+        <v>1</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="I46" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="40.5">
+      <c r="A47" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D47" s="4">
+        <v>1</v>
+      </c>
+      <c r="E47" s="4">
+        <v>1</v>
+      </c>
+      <c r="F47" s="4">
+        <v>1</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="I47" s="4">
         <v>1</v>
       </c>
     </row>
